--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
@@ -785,19 +785,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -816,6 +816,8 @@
 Mörk kolflarnlav
 Orange taggsvamp
 Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallfingersvamp
 Talltagel
 Talltita
 Tretåig hackspett
@@ -883,7 +885,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1022,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1155,7 +1157,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1289,7 +1291,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1423,7 @@
         <v>44969</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1550,7 +1552,7 @@
         <v>45226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1679,7 +1681,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1812,7 +1814,7 @@
         <v>45894</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1946,7 @@
         <v>45425</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2072,7 +2074,7 @@
         <v>45470</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2199,7 +2201,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2320,7 +2322,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2445,7 +2447,7 @@
         <v>45554</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2568,7 +2570,7 @@
         <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2692,7 +2694,7 @@
         <v>46178</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2812,7 +2814,7 @@
         <v>45013</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2940,7 +2942,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3067,7 +3069,7 @@
         <v>44739</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3178,7 +3180,7 @@
         <v>44630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3293,7 +3295,7 @@
         <v>46247</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3415,7 @@
         <v>45470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3529,7 +3531,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3649,7 +3651,7 @@
         <v>45775</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3764,7 +3766,7 @@
         <v>45944</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3879,7 +3881,7 @@
         <v>44463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3989,7 +3991,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4104,7 +4106,7 @@
         <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4218,7 +4220,7 @@
         <v>45573</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4332,7 +4334,7 @@
         <v>46105</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4450,7 +4452,7 @@
         <v>44552</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4566,7 +4568,7 @@
         <v>46164</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4679,7 +4681,7 @@
         <v>45960</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4792,7 +4794,7 @@
         <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4905,7 +4907,7 @@
         <v>46211</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5018,7 +5020,7 @@
         <v>46260</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5131,7 +5133,7 @@
         <v>46272</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5244,7 +5246,7 @@
         <v>46272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5357,7 +5359,7 @@
         <v>45819</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5470,7 +5472,7 @@
         <v>45576</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5582,7 +5584,7 @@
         <v>45600</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5694,7 +5696,7 @@
         <v>46195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5806,7 +5808,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5918,7 +5920,7 @@
         <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6025,7 +6027,7 @@
         <v>46210</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6132,7 +6134,7 @@
         <v>46211</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6244,7 +6246,7 @@
         <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6356,7 +6358,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6468,7 +6470,7 @@
         <v>45846</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6580,7 +6582,7 @@
         <v>44671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6691,7 +6693,7 @@
         <v>44874</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6802,7 +6804,7 @@
         <v>45407</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6913,7 +6915,7 @@
         <v>45621</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7024,7 +7026,7 @@
         <v>45932</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7135,7 +7137,7 @@
         <v>45944</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7246,7 +7248,7 @@
         <v>45980</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7357,7 +7359,7 @@
         <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7468,7 +7470,7 @@
         <v>45516</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7579,7 +7581,7 @@
         <v>46164</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7690,7 +7692,7 @@
         <v>45450</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7801,7 +7803,7 @@
         <v>46195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7912,7 +7914,7 @@
         <v>45576</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8018,7 +8020,7 @@
         <v>45028</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8129,7 +8131,7 @@
         <v>44813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8239,7 +8241,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8353,7 +8355,7 @@
         <v>45922</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8463,7 +8465,7 @@
         <v>45922</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8568,7 +8570,7 @@
         <v>45623</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8678,7 +8680,7 @@
         <v>46147</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8788,7 +8790,7 @@
         <v>46147</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8898,7 +8900,7 @@
         <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9003,7 +9005,7 @@
         <v>45944</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9113,7 +9115,7 @@
         <v>46150</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9223,7 +9225,7 @@
         <v>45953</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9333,7 +9335,7 @@
         <v>45957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9443,7 +9445,7 @@
         <v>45960</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9553,7 +9555,7 @@
         <v>45989</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9663,7 +9665,7 @@
         <v>45993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9773,7 +9775,7 @@
         <v>46164</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9883,7 +9885,7 @@
         <v>44832</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9993,7 +9995,7 @@
         <v>46184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10103,7 +10105,7 @@
         <v>45953</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10213,7 +10215,7 @@
         <v>46197</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10323,7 +10325,7 @@
         <v>46197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10432,7 +10434,7 @@
         <v>46197</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10541,7 +10543,7 @@
         <v>46261</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10651,7 +10653,7 @@
         <v>46267</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10761,7 +10763,7 @@
         <v>45793</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10871,7 +10873,7 @@
         <v>45840</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10985,7 +10987,7 @@
         <v>45847</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11095,7 +11097,7 @@
         <v>45565</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11200,7 +11202,7 @@
         <v>45629</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11305,7 +11307,7 @@
         <v>44735</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11383,7 +11385,7 @@
         <v>44868</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11456,7 +11458,7 @@
         <v>44552</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11529,7 +11531,7 @@
         <v>44491</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11607,7 +11609,7 @@
         <v>44491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11685,7 +11687,7 @@
         <v>44460</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11758,7 +11760,7 @@
         <v>44522</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11831,7 +11833,7 @@
         <v>44552</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11904,7 +11906,7 @@
         <v>44484</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11977,7 +11979,7 @@
         <v>44847</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12050,7 +12052,7 @@
         <v>44825</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12123,7 +12125,7 @@
         <v>44741</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12196,7 +12198,7 @@
         <v>44463</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12274,7 +12276,7 @@
         <v>44750</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12347,7 +12349,7 @@
         <v>44602</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12420,7 +12422,7 @@
         <v>44515</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12493,7 +12495,7 @@
         <v>44819</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12566,7 +12568,7 @@
         <v>44795</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12639,7 +12641,7 @@
         <v>44813</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12717,7 +12719,7 @@
         <v>44476</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12790,7 +12792,7 @@
         <v>44677</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12863,7 +12865,7 @@
         <v>45078</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12936,7 +12938,7 @@
         <v>45554</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13009,7 +13011,7 @@
         <v>45622</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13087,7 +13089,7 @@
         <v>44959</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13160,7 +13162,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13233,7 +13235,7 @@
         <v>44732</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13306,7 +13308,7 @@
         <v>44460</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13379,7 +13381,7 @@
         <v>45583</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13457,7 +13459,7 @@
         <v>44728</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13530,7 +13532,7 @@
         <v>44855</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13603,7 +13605,7 @@
         <v>45016</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13676,7 +13678,7 @@
         <v>45552</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13754,7 +13756,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13832,7 +13834,7 @@
         <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13905,7 +13907,7 @@
         <v>45576</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13978,7 +13980,7 @@
         <v>45125</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14051,7 +14053,7 @@
         <v>45561</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14129,7 +14131,7 @@
         <v>45220</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14207,7 +14209,7 @@
         <v>45265</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14285,7 +14287,7 @@
         <v>45280</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14358,7 +14360,7 @@
         <v>45511</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14431,7 +14433,7 @@
         <v>44967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14504,7 +14506,7 @@
         <v>44895</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14582,7 +14584,7 @@
         <v>45510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14655,7 +14657,7 @@
         <v>45709</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14728,7 +14730,7 @@
         <v>45989</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14801,7 +14803,7 @@
         <v>45554</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14874,7 +14876,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14947,7 +14949,7 @@
         <v>44460</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15020,7 +15022,7 @@
         <v>45280</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15093,7 +15095,7 @@
         <v>45885</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15166,7 +15168,7 @@
         <v>45434</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15239,7 +15241,7 @@
         <v>45895</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15317,7 +15319,7 @@
         <v>44494</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15390,7 +15392,7 @@
         <v>44949</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15463,7 +15465,7 @@
         <v>45896</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15541,7 +15543,7 @@
         <v>45896</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15619,7 +15621,7 @@
         <v>45334</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15692,7 +15694,7 @@
         <v>45580</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15765,7 +15767,7 @@
         <v>45629</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15838,7 +15840,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15916,7 +15918,7 @@
         <v>45874</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15989,7 +15991,7 @@
         <v>44942</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16062,7 +16064,7 @@
         <v>45365</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16135,7 +16137,7 @@
         <v>45916</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16208,7 +16210,7 @@
         <v>45916</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16281,7 +16283,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16354,7 +16356,7 @@
         <v>45919</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16427,7 +16429,7 @@
         <v>45925</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16500,7 +16502,7 @@
         <v>45925</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16573,7 +16575,7 @@
         <v>45678</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16646,7 +16648,7 @@
         <v>45929</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16724,7 +16726,7 @@
         <v>45931</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16802,7 +16804,7 @@
         <v>45932</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16880,7 +16882,7 @@
         <v>45933</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16958,7 +16960,7 @@
         <v>45642</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17031,7 +17033,7 @@
         <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17104,7 +17106,7 @@
         <v>46147</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17182,7 +17184,7 @@
         <v>45938</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17255,7 +17257,7 @@
         <v>45938</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17333,7 +17335,7 @@
         <v>45579</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17411,7 +17413,7 @@
         <v>45735</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17484,7 +17486,7 @@
         <v>45945</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17557,7 +17559,7 @@
         <v>46148</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17635,7 +17637,7 @@
         <v>45947</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17713,7 +17715,7 @@
         <v>45946</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17786,7 +17788,7 @@
         <v>45607</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17864,7 +17866,7 @@
         <v>45691</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17937,7 +17939,7 @@
         <v>46153</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18015,7 +18017,7 @@
         <v>45950</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18088,7 +18090,7 @@
         <v>45167</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18161,7 +18163,7 @@
         <v>46150</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18239,7 +18241,7 @@
         <v>46153</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18317,7 +18319,7 @@
         <v>46150</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18390,7 +18392,7 @@
         <v>46150</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18463,7 +18465,7 @@
         <v>44617</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18536,7 +18538,7 @@
         <v>45957</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18614,7 +18616,7 @@
         <v>45078</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18687,7 +18689,7 @@
         <v>46150</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18765,7 +18767,7 @@
         <v>46150</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18843,7 +18845,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18921,7 +18923,7 @@
         <v>45961</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18999,7 +19001,7 @@
         <v>44895</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19077,7 +19079,7 @@
         <v>45961</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19155,7 +19157,7 @@
         <v>45068</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19228,7 +19230,7 @@
         <v>45960</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19306,7 +19308,7 @@
         <v>44910</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19379,7 +19381,7 @@
         <v>45964</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19452,7 +19454,7 @@
         <v>46154</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19530,7 +19532,7 @@
         <v>44942</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19603,7 +19605,7 @@
         <v>45224</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19681,7 +19683,7 @@
         <v>45972</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19759,7 +19761,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19832,7 +19834,7 @@
         <v>45973</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19910,7 +19912,7 @@
         <v>45972</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19988,7 +19990,7 @@
         <v>44617</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20061,7 +20063,7 @@
         <v>45975</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20139,7 +20141,7 @@
         <v>45974</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20232,7 +20234,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20310,7 +20312,7 @@
         <v>45974</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20403,7 +20405,7 @@
         <v>45044</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20476,7 +20478,7 @@
         <v>45979</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20549,7 +20551,7 @@
         <v>45980</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20627,7 +20629,7 @@
         <v>45987</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20700,7 +20702,7 @@
         <v>45708</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20778,7 +20780,7 @@
         <v>45986</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20856,7 +20858,7 @@
         <v>45987</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20934,7 +20936,7 @@
         <v>45986</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21012,7 +21014,7 @@
         <v>45271</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21090,7 +21092,7 @@
         <v>46161</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21168,7 +21170,7 @@
         <v>45992</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21241,7 +21243,7 @@
         <v>46160</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21314,7 +21316,7 @@
         <v>44918</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21387,7 +21389,7 @@
         <v>44918</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21460,7 +21462,7 @@
         <v>45992</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21533,7 +21535,7 @@
         <v>45992</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21611,7 +21613,7 @@
         <v>45992</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21684,7 +21686,7 @@
         <v>45992</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21757,7 +21759,7 @@
         <v>45232</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21830,7 +21832,7 @@
         <v>46160</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21903,7 +21905,7 @@
         <v>46160</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21976,7 +21978,7 @@
         <v>46160</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22049,7 +22051,7 @@
         <v>46160</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22122,7 +22124,7 @@
         <v>45583</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22200,7 +22202,7 @@
         <v>45548</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22278,7 +22280,7 @@
         <v>46163</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22356,7 +22358,7 @@
         <v>44985</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22429,7 +22431,7 @@
         <v>46164</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22507,7 +22509,7 @@
         <v>45639</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22585,7 +22587,7 @@
         <v>45961</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22663,7 +22665,7 @@
         <v>45337</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22741,7 +22743,7 @@
         <v>45302</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22814,7 +22816,7 @@
         <v>44872</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22887,7 +22889,7 @@
         <v>45632</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22960,7 +22962,7 @@
         <v>44460</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23033,7 +23035,7 @@
         <v>45933</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23106,7 +23108,7 @@
         <v>46019</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23179,7 +23181,7 @@
         <v>46019</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23252,7 +23254,7 @@
         <v>46019</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23325,7 +23327,7 @@
         <v>45688</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23398,7 +23400,7 @@
         <v>45548</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23476,7 +23478,7 @@
         <v>45960</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23554,7 +23556,7 @@
         <v>45365</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23627,7 +23629,7 @@
         <v>46174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23700,7 +23702,7 @@
         <v>45305</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23773,7 +23775,7 @@
         <v>44580</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23846,7 +23848,7 @@
         <v>44873</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23919,7 +23921,7 @@
         <v>44847</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23992,7 +23994,7 @@
         <v>46050</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24070,7 +24072,7 @@
         <v>46176</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24148,7 +24150,7 @@
         <v>45344</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24221,7 +24223,7 @@
         <v>46055</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24294,7 +24296,7 @@
         <v>46177</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24372,7 +24374,7 @@
         <v>45470</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24450,7 +24452,7 @@
         <v>45565</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24528,7 +24530,7 @@
         <v>45565</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24606,7 +24608,7 @@
         <v>45463</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24679,7 +24681,7 @@
         <v>46182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24752,7 +24754,7 @@
         <v>46183</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24830,7 +24832,7 @@
         <v>45098</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24903,7 +24905,7 @@
         <v>46185</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24981,7 +24983,7 @@
         <v>45296</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25054,7 +25056,7 @@
         <v>46189</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25132,7 +25134,7 @@
         <v>46191</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25205,7 +25207,7 @@
         <v>46191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25278,7 +25280,7 @@
         <v>46191</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25351,7 +25353,7 @@
         <v>46191</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25424,7 +25426,7 @@
         <v>44952</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25497,7 +25499,7 @@
         <v>46191</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25570,7 +25572,7 @@
         <v>46191</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25643,7 +25645,7 @@
         <v>45552</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25716,7 +25718,7 @@
         <v>46196</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25789,7 +25791,7 @@
         <v>46106</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25862,7 +25864,7 @@
         <v>46106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25940,7 +25942,7 @@
         <v>44617</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26013,7 +26015,7 @@
         <v>46198</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26086,7 +26088,7 @@
         <v>46198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26159,7 +26161,7 @@
         <v>46197</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26237,7 +26239,7 @@
         <v>46106</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26310,7 +26312,7 @@
         <v>44491</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26383,7 +26385,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26456,7 +26458,7 @@
         <v>46197</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26529,7 +26531,7 @@
         <v>46197</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26602,7 +26604,7 @@
         <v>45511</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26675,7 +26677,7 @@
         <v>45278</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26748,7 +26750,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26821,7 +26823,7 @@
         <v>45632</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26894,7 +26896,7 @@
         <v>46197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26972,7 +26974,7 @@
         <v>44994</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27045,7 +27047,7 @@
         <v>46202</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27118,7 +27120,7 @@
         <v>46112</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27191,7 +27193,7 @@
         <v>45477</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27269,7 +27271,7 @@
         <v>45642</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27342,7 +27344,7 @@
         <v>45979</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27415,7 +27417,7 @@
         <v>45114</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27488,7 +27490,7 @@
         <v>45484</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27566,7 +27568,7 @@
         <v>46122</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27639,7 +27641,7 @@
         <v>46122</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27712,7 +27714,7 @@
         <v>46122</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27785,7 +27787,7 @@
         <v>46122</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27858,7 +27860,7 @@
         <v>46126</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27931,7 +27933,7 @@
         <v>46202</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28004,7 +28006,7 @@
         <v>46245</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28077,7 +28079,7 @@
         <v>46202</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28150,7 +28152,7 @@
         <v>46199</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28228,7 +28230,7 @@
         <v>45252</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28301,7 +28303,7 @@
         <v>44943</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28379,7 +28381,7 @@
         <v>46132</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28452,7 +28454,7 @@
         <v>44810</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28530,7 +28532,7 @@
         <v>46203</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28608,7 +28610,7 @@
         <v>44873</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28681,7 +28683,7 @@
         <v>46246</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28754,7 +28756,7 @@
         <v>45282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28832,7 +28834,7 @@
         <v>44823</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28910,7 +28912,7 @@
         <v>45334</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28983,7 +28985,7 @@
         <v>45938</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29061,7 +29063,7 @@
         <v>45904</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29139,7 +29141,7 @@
         <v>45709</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29212,7 +29214,7 @@
         <v>44790</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29285,7 +29287,7 @@
         <v>46246</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29363,7 +29365,7 @@
         <v>45603</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29436,7 +29438,7 @@
         <v>45406</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29509,7 +29511,7 @@
         <v>46246</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29582,7 +29584,7 @@
         <v>46204</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29655,7 +29657,7 @@
         <v>45251</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29728,7 +29730,7 @@
         <v>45162</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29801,7 +29803,7 @@
         <v>45494</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29879,7 +29881,7 @@
         <v>45246</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29952,7 +29954,7 @@
         <v>46254</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30030,7 +30032,7 @@
         <v>44896</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30103,7 +30105,7 @@
         <v>46254</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30181,7 +30183,7 @@
         <v>45266</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30254,7 +30256,7 @@
         <v>46213</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30332,7 +30334,7 @@
         <v>45688</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30405,7 +30407,7 @@
         <v>45016</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30478,7 +30480,7 @@
         <v>44617</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30551,7 +30553,7 @@
         <v>44617</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30624,7 +30626,7 @@
         <v>45334</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30697,7 +30699,7 @@
         <v>45495</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30775,7 +30777,7 @@
         <v>46196</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30848,7 +30850,7 @@
         <v>45216</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30921,7 +30923,7 @@
         <v>45194</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30994,7 +30996,7 @@
         <v>45448</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31067,7 +31069,7 @@
         <v>45644</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31140,7 +31142,7 @@
         <v>46267</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31218,7 +31220,7 @@
         <v>46267</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31296,7 +31298,7 @@
         <v>45434</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31369,7 +31371,7 @@
         <v>45992</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31442,7 +31444,7 @@
         <v>46252</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31520,7 +31522,7 @@
         <v>46191</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31593,7 +31595,7 @@
         <v>46230</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31666,7 +31668,7 @@
         <v>46272</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31739,7 +31741,7 @@
         <v>45772</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31812,7 +31814,7 @@
         <v>45784</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31890,7 +31892,7 @@
         <v>45601</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31963,7 +31965,7 @@
         <v>46279</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32036,7 +32038,7 @@
         <v>45478</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32109,7 +32111,7 @@
         <v>46084</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32182,7 +32184,7 @@
         <v>45791</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32255,7 +32257,7 @@
         <v>45792</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32333,7 +32335,7 @@
         <v>46239</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32406,7 +32408,7 @@
         <v>46283</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32479,7 +32481,7 @@
         <v>45525</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32557,7 +32559,7 @@
         <v>45803</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32630,7 +32632,7 @@
         <v>45782</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32703,7 +32705,7 @@
         <v>45804</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32781,7 +32783,7 @@
         <v>45805</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32859,7 +32861,7 @@
         <v>45808</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32937,7 +32939,7 @@
         <v>45220</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33015,7 +33017,7 @@
         <v>45812</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33088,7 +33090,7 @@
         <v>45222</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33161,7 +33163,7 @@
         <v>45561</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33234,7 +33236,7 @@
         <v>45821</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33307,7 +33309,7 @@
         <v>45505</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33380,7 +33382,7 @@
         <v>45827</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33458,7 +33460,7 @@
         <v>45831</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33536,7 +33538,7 @@
         <v>45833</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33609,7 +33611,7 @@
         <v>44462</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33682,7 +33684,7 @@
         <v>44741</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33755,7 +33757,7 @@
         <v>45869</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33828,7 +33830,7 @@
         <v>45831</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33901,7 +33903,7 @@
         <v>45874</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33979,7 +33981,7 @@
         <v>45772</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34052,7 +34054,7 @@
         <v>45478</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34125,7 +34127,7 @@
         <v>44945</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34203,7 +34205,7 @@
         <v>45686</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34276,7 +34278,7 @@
         <v>45792</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34354,7 +34356,7 @@
         <v>45436</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34427,7 +34429,7 @@
         <v>45961</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34505,7 +34507,7 @@
         <v>45961</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34583,7 +34585,7 @@
         <v>45961</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34661,7 +34663,7 @@
         <v>45960</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34739,7 +34741,7 @@
         <v>46070</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34812,7 +34814,7 @@
         <v>46168</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34885,7 +34887,7 @@
         <v>46178</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34958,7 +34960,7 @@
         <v>46178</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35031,7 +35033,7 @@
         <v>46181</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35109,7 +35111,7 @@
         <v>46185</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45226</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44969</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45425</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>45470</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>46273</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45789</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45554</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>46178</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45013</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44739</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>45470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>46273</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>46247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44630</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45944</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>46105</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45573</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44552</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>46164</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>45960</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>46211</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>46210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>46260</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>46272</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>45846</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45576</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>46195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>46211</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>46210</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>46210</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44671</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>45576</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45944</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45450</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>46164</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>46195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>45516</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45407</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>45028</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>44813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45922</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45938</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45953</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45957</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45960</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>45623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45989</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45993</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45922</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46147</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>46147</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>46150</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45840</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>46164</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45847</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>46184</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>46197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>46197</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>46197</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44832</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>46267</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45793</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44868</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44491</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44491</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44522</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44484</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44847</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44750</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44602</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44515</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44819</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44795</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44813</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>44476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45334</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45334</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45232</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45434</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45365</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45365</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44952</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45554</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44847</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45463</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>46019</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>46019</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>46019</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45933</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45688</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45271</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45477</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44873</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45265</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45525</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45561</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45885</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45960</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45629</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44895</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45895</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45896</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45896</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45622</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>46050</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45511</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>46055</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45916</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45916</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45919</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45782</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45803</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45510</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>44580</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44677</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45804</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45691</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45925</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45925</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45565</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>44910</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45932</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44943</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45808</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45252</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45931</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45933</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45936</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45220</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45938</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45344</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45946</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45945</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45950</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45947</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>45583</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45222</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45812</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>46106</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>46106</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>46106</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44732</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45957</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>46112</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45960</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45979</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45961</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>44851</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45961</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45964</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>46122</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>46122</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46122</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46122</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45972</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45561</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45973</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45974</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45974</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>46132</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45975</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45975</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45980</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45979</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45511</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>45986</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45266</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45162</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45565</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45987</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45708</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45078</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45992</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45992</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45992</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45992</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45632</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45642</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45709</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45250</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45961</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45938</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45953</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45989</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44823</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45821</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44494</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45505</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45334</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45904</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45874</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45044</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45709</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44810</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45827</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45098</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45678</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44967</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46148</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>46147</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46150</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>46150</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>46150</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>46150</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46150</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44918</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>46153</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44918</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>46154</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45833</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>46153</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44896</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>46160</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45495</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>46160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44873</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>46160</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>46160</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46160</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45735</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46163</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>46164</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45576</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45282</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44741</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44942</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45305</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>46177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>46176</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45869</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45874</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45639</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>46183</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>46182</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45068</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>46185</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45167</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45583</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>46189</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45831</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45552</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>46191</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>46191</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>46191</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>46191</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45644</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>46197</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>46197</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>46197</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>46196</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>46197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45772</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46198</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45337</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>44552</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>46199</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45484</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>46202</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>46203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46202</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46202</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45434</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>46204</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44617</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>44617</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>46254</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>46213</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>46254</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45194</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>44728</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45224</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45278</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>46196</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44790</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45280</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>46267</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45296</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>46267</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46272</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>46191</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>46230</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>44855</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>45016</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>45016</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>45494</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>44795</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>46279</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>46239</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45688</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>45406</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45302</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>46283</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>44994</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45548</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>45470</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>46288</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>46126</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>46198</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>46245</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45078</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>46246</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45448</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>44942</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>46246</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45246</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>44959</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45603</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>46246</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44491</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>44617</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>45114</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44949</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45554</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45125</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45548</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44872</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>44617</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>45216</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45632</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45220</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45607</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45580</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45579</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45642</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45772</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45784</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45478</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45601</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45792</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45791</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45478</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45686</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45792</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45436</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45960</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45961</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45961</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45961</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>46070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>46168</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>46178</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>46178</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>46181</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>46185</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45947</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>45226</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44969</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45425</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>45470</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>46273</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45789</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45554</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>46178</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45013</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>44739</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>45470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>46273</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>46247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44630</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45944</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>46105</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45573</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44552</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>46164</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>45960</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>46211</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>46210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>46260</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>46272</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>45846</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45576</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>46195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>46211</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>46210</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>46210</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44671</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>45576</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45944</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45980</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45450</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>46164</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>46195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>45516</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45407</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>45028</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>44813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45922</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45938</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45953</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45957</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45960</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>45623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45989</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45993</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45922</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46147</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>46147</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>46150</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45840</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>46164</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45847</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>46184</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>46197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>46197</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>46197</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44832</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>46267</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45793</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44868</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44491</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44491</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44522</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44484</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44847</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44750</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44602</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44515</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44819</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44795</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44813</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>44476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45334</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45334</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45232</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45434</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45365</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45365</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44952</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45554</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44847</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45463</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>46019</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>46019</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>46019</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45933</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45688</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45271</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45477</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44873</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45265</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45525</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45561</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45885</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45960</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45629</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44895</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45895</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45896</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45896</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45622</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45280</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>46050</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45511</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>46055</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45916</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45916</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45919</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45782</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45803</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45510</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>44580</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44677</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45804</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45691</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45925</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45925</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45565</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>44910</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45932</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44943</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45808</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45252</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45931</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45933</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45936</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45220</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45938</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45344</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45946</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45945</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45950</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45947</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>45583</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45222</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45812</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>46106</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>46106</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>46106</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44732</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45957</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>46112</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45960</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45979</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45961</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>44851</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45961</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45964</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>46122</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>46122</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46122</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46122</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45972</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45561</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45973</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45974</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45974</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>46132</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45975</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45975</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45980</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45979</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45511</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>45986</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45266</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45162</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45565</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45987</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45708</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45078</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45992</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45992</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45992</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45992</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45632</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45642</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45709</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45250</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45961</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45938</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45953</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45989</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44823</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45821</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44494</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45505</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45334</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45904</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45874</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45044</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45709</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44810</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45827</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45098</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45678</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44967</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46148</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>46147</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46150</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>46150</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>46150</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>46150</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46150</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44918</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>46153</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44918</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>46154</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45833</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>46153</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44896</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>46160</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45495</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>46160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44873</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>46160</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>46160</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46160</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45735</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46163</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>46164</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45576</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45282</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44741</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44942</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45305</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>46177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>46176</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45869</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45874</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45639</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>46183</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>46182</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45068</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>46185</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45167</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45583</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>46189</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45831</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45552</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>46191</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>46191</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>46191</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>46191</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45644</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>46197</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>46197</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>46197</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>46196</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>46197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>46198</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45772</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46198</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45337</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>44552</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>46199</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45484</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>46202</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>46203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46202</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46202</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45434</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>46204</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44617</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>44617</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>46254</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>46213</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>46254</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45194</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>44728</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45224</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45278</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>46196</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44790</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45280</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>46267</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45296</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>46267</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46272</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>46191</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>46230</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>44855</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>45016</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>45016</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>45494</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>44795</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>46279</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>46239</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45688</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>45406</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45302</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>46283</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>44994</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45548</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>45470</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>46288</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>46126</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>46198</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>46245</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45078</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>46246</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45448</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>44942</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>46246</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45246</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>44959</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45603</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>46246</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44491</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>44617</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>45114</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44949</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45554</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45125</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45548</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44872</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>44617</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>45216</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45632</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45220</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45607</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45580</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45579</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45642</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45772</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45784</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45478</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45601</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45792</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45791</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45478</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45686</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45792</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45436</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45960</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45961</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45961</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45961</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>46070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>46168</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>46178</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>46178</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>46181</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>46185</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 56243-2024</t>
+          <t>A 51047-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45624</v>
+        <v>45947</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,20 +613,25 @@
           <t>ÄLVSBYN</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>3.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,21 +643,164 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="T2" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="U2" t="n">
         <v>58</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Grenlav
+Smultronkantarell
+Spadskinn
+Tajgataggsvamp
+Torrmusseron
+Blanksvart spiklav
+Blå taggsvamp
+Blågrå svartspik
+Brunpudrad nållav
+Dropptaggsvamp
+Dvärgbägarlav
+Kolflarnlav
+Lavskrika
+Mjölsvärting
+Motaggsvamp
+Mörk kolflarnlav
+Orange taggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallfingersvamp
+Tallriska
+Talltagel
+Talltita
+Tretåig hackspett
+Vaxspindling
+Vedskivlav
+Vitplätt
+Gullgröppa
+Nästlav
+Plattlummer
+Svart taggsvamp agg.
+Tjäder
+Tofsmes
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 51047-2025 artfynd.xlsx", "A 51047-2025")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 51047-2025 karta.png", "A 51047-2025")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 51047-2025 georefererad karta.tif", "A 51047-2025")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 51047-2025 FSC-klagomål.docx", "A 51047-2025")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 51047-2025 FSC-klagomål mail.docx", "A 51047-2025")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 51047-2025 tillsynsbegäran.docx", "A 51047-2025")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 51047-2025 tillsynsbegäran mail.docx", "A 51047-2025")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/fåglar/A 51047-2025 prioriterade fågelarter.docx", "A 51047-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 56243-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45624</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>19</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="n">
+        <v>66</v>
+      </c>
+      <c r="U3" t="n">
+        <v>59</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -686,182 +834,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 56243-2024 artfynd.xlsx", "A 56243-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 56243-2024 karta.png", "A 56243-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 56243-2024 georefererad karta.tif", "A 56243-2024")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/knärot/A 56243-2024 karta knärot.png", "A 56243-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 56243-2024 FSC-klagomål.docx", "A 56243-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 56243-2024 FSC-klagomål mail.docx", "A 56243-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 56243-2024 tillsynsbegäran.docx", "A 56243-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 56243-2024 tillsynsbegäran mail.docx", "A 56243-2024")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/fåglar/A 56243-2024 prioriterade fågelarter.docx", "A 56243-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 51047-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45947</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>20</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>23</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>29</v>
-      </c>
-      <c r="T3" t="n">
-        <v>60</v>
-      </c>
-      <c r="U3" t="n">
-        <v>46</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Grenlav
-Smultronkantarell
-Blanksvart spiklav
-Blå taggsvamp
-Blågrå svartspik
-Brunpudrad nållav
-Dropptaggsvamp
-Dvärgbägarlav
-Kolflarnlav
-Lavskrika
-Motaggsvamp
-Mörk kolflarnlav
-Orange taggsvamp
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallfingersvamp
-Talltagel
-Talltita
-Tretåig hackspett
-Vaxspindling
-Vedskivlav
-Vitplätt
-Gullgröppa
-Nästlav
-Svart taggsvamp agg.
-Tjäder
-Tofsmes
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 51047-2025 artfynd.xlsx", "A 51047-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 51047-2025 karta.png", "A 51047-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 51047-2025 georefererad karta.tif", "A 51047-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 51047-2025 FSC-klagomål.docx", "A 51047-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 51047-2025 FSC-klagomål mail.docx", "A 51047-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 51047-2025 tillsynsbegäran.docx", "A 51047-2025")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 51047-2025 tillsynsbegäran mail.docx", "A 51047-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/fåglar/A 51047-2025 prioriterade fågelarter.docx", "A 51047-2025")</f>
         <v/>
       </c>
     </row>
@@ -885,7 +891,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1022,7 +1028,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1163,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1291,7 +1297,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1429,7 @@
         <v>44969</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1558,7 @@
         <v>45226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1687,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1814,7 +1820,7 @@
         <v>46297</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1943,7 +1949,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2075,7 +2081,7 @@
         <v>45425</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2203,7 +2209,7 @@
         <v>45470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2330,7 +2336,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2455,7 +2461,7 @@
         <v>45789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2576,7 +2582,7 @@
         <v>45554</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2699,7 +2705,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2823,7 +2829,7 @@
         <v>46178</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2943,7 +2949,7 @@
         <v>45013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3071,7 +3077,7 @@
         <v>45940</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3198,7 +3204,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3309,7 +3315,7 @@
         <v>45775</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3424,7 +3430,7 @@
         <v>44630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3539,7 +3545,7 @@
         <v>45470</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3655,7 +3661,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3775,7 +3781,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3895,7 +3901,7 @@
         <v>45944</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4010,7 +4016,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4125,7 +4131,7 @@
         <v>46297</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4244,7 +4250,7 @@
         <v>45960</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4358,7 +4364,7 @@
         <v>46105</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4476,7 +4482,7 @@
         <v>45573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4590,7 +4596,7 @@
         <v>44552</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4706,7 +4712,7 @@
         <v>45819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4819,7 +4825,7 @@
         <v>46164</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4932,7 +4938,7 @@
         <v>45960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5045,7 +5051,7 @@
         <v>46210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5158,7 +5164,7 @@
         <v>46211</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5271,7 +5277,7 @@
         <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5384,7 +5390,7 @@
         <v>46272</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5497,7 +5503,7 @@
         <v>46272</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5610,7 +5616,7 @@
         <v>45789</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5722,7 +5728,7 @@
         <v>45576</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5834,7 +5840,7 @@
         <v>45846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5946,7 +5952,7 @@
         <v>45600</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6058,7 +6064,7 @@
         <v>46195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6170,7 +6176,7 @@
         <v>46206</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6282,7 +6288,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6389,7 +6395,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6496,7 +6502,7 @@
         <v>46211</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6608,7 +6614,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6720,7 +6726,7 @@
         <v>44671</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6831,7 +6837,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6942,7 +6948,7 @@
         <v>45407</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7053,7 +7059,7 @@
         <v>45944</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7164,7 +7170,7 @@
         <v>45980</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7275,7 +7281,7 @@
         <v>45621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7386,7 +7392,7 @@
         <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7497,7 +7503,7 @@
         <v>45574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7608,7 +7614,7 @@
         <v>45516</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7719,7 +7725,7 @@
         <v>45450</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7830,7 +7836,7 @@
         <v>46195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7941,7 +7947,7 @@
         <v>45576</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8047,7 +8053,7 @@
         <v>45028</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8158,7 +8164,7 @@
         <v>44813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8268,7 +8274,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8382,7 +8388,7 @@
         <v>45922</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8487,7 +8493,7 @@
         <v>45938</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8592,7 +8598,7 @@
         <v>45944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8702,7 +8708,7 @@
         <v>45953</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8812,7 +8818,7 @@
         <v>45957</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8922,7 +8928,7 @@
         <v>45960</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9032,7 +9038,7 @@
         <v>45953</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9142,7 +9148,7 @@
         <v>45989</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9252,7 +9258,7 @@
         <v>45993</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9362,7 +9368,7 @@
         <v>45840</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9476,7 +9482,7 @@
         <v>45847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9586,7 +9592,7 @@
         <v>45565</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9691,7 +9697,7 @@
         <v>45623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9801,7 +9807,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9911,7 +9917,7 @@
         <v>45629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10016,7 +10022,7 @@
         <v>46147</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10126,7 +10132,7 @@
         <v>46147</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10236,7 +10242,7 @@
         <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10346,7 +10352,7 @@
         <v>46164</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10456,7 +10462,7 @@
         <v>46184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10566,7 +10572,7 @@
         <v>46197</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10676,7 +10682,7 @@
         <v>46197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10785,7 +10791,7 @@
         <v>46197</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10894,7 +10900,7 @@
         <v>44832</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11004,7 +11010,7 @@
         <v>46261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11114,7 +11120,7 @@
         <v>46267</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11224,7 +11230,7 @@
         <v>45793</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11334,7 +11340,7 @@
         <v>46297</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11444,7 +11450,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11522,7 +11528,7 @@
         <v>44868</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11595,7 +11601,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11668,7 +11674,7 @@
         <v>44491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11746,7 +11752,7 @@
         <v>44491</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11824,7 +11830,7 @@
         <v>44522</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11897,7 +11903,7 @@
         <v>44552</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11970,7 +11976,7 @@
         <v>44484</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12043,7 +12049,7 @@
         <v>44847</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12116,7 +12122,7 @@
         <v>44825</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12189,7 +12195,7 @@
         <v>44741</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12262,7 +12268,7 @@
         <v>44750</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12335,7 +12341,7 @@
         <v>44602</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12408,7 +12414,7 @@
         <v>44515</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12481,7 +12487,7 @@
         <v>44819</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12554,7 +12560,7 @@
         <v>44795</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12627,7 +12633,7 @@
         <v>44813</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12705,7 +12711,7 @@
         <v>44476</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12778,7 +12784,7 @@
         <v>45554</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12851,7 +12857,7 @@
         <v>45078</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12924,7 +12930,7 @@
         <v>45622</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13002,7 +13008,7 @@
         <v>44677</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13075,7 +13081,7 @@
         <v>44959</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13148,7 +13154,7 @@
         <v>44732</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13221,7 +13227,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13294,7 +13300,7 @@
         <v>45478</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13367,7 +13373,7 @@
         <v>45961</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13445,7 +13451,7 @@
         <v>45629</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13518,7 +13524,7 @@
         <v>45583</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13596,7 +13602,7 @@
         <v>44728</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13669,7 +13675,7 @@
         <v>45791</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13742,7 +13748,7 @@
         <v>45933</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13815,7 +13821,7 @@
         <v>46019</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13888,7 +13894,7 @@
         <v>46019</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13961,7 +13967,7 @@
         <v>46019</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14034,7 +14040,7 @@
         <v>45688</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14107,7 +14113,7 @@
         <v>45895</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14185,7 +14191,7 @@
         <v>45896</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14263,7 +14269,7 @@
         <v>45896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14341,7 +14347,7 @@
         <v>44855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14414,7 +14420,7 @@
         <v>45792</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14492,7 +14498,7 @@
         <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14570,7 +14576,7 @@
         <v>45016</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14643,7 +14649,7 @@
         <v>45525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14721,7 +14727,7 @@
         <v>45916</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14794,7 +14800,7 @@
         <v>45916</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14867,7 +14873,7 @@
         <v>46050</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14945,7 +14951,7 @@
         <v>45919</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15018,7 +15024,7 @@
         <v>45803</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15091,7 +15097,7 @@
         <v>45919</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15164,7 +15170,7 @@
         <v>45782</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15237,7 +15243,7 @@
         <v>45552</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15315,7 +15321,7 @@
         <v>45804</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15393,7 +15399,7 @@
         <v>45805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15471,7 +15477,7 @@
         <v>46055</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15544,7 +15550,7 @@
         <v>45925</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15617,7 +15623,7 @@
         <v>45925</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15690,7 +15696,7 @@
         <v>45929</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15768,7 +15774,7 @@
         <v>45931</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15846,7 +15852,7 @@
         <v>45932</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15924,7 +15930,7 @@
         <v>45933</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16002,7 +16008,7 @@
         <v>45936</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16075,7 +16081,7 @@
         <v>45808</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16153,7 +16159,7 @@
         <v>44552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16231,7 +16237,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16304,7 +16310,7 @@
         <v>45938</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16382,7 +16388,7 @@
         <v>45220</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16460,7 +16466,7 @@
         <v>45945</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16533,7 +16539,7 @@
         <v>45947</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16611,7 +16617,7 @@
         <v>45946</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16684,7 +16690,7 @@
         <v>45950</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16757,7 +16763,7 @@
         <v>45812</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16830,7 +16836,7 @@
         <v>44851</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16903,7 +16909,7 @@
         <v>45957</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16981,7 +16987,7 @@
         <v>45576</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17054,7 +17060,7 @@
         <v>45222</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17127,7 +17133,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17205,7 +17211,7 @@
         <v>45961</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17283,7 +17289,7 @@
         <v>45961</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17361,7 +17367,7 @@
         <v>45960</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17439,7 +17445,7 @@
         <v>45964</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17512,7 +17518,7 @@
         <v>45561</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17590,7 +17596,7 @@
         <v>45561</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17663,7 +17669,7 @@
         <v>45125</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17736,7 +17742,7 @@
         <v>45220</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17814,7 +17820,7 @@
         <v>45972</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17892,7 +17898,7 @@
         <v>45973</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17970,7 +17976,7 @@
         <v>45511</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18043,7 +18049,7 @@
         <v>45972</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18121,7 +18127,7 @@
         <v>45265</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18199,7 +18205,7 @@
         <v>45975</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18277,7 +18283,7 @@
         <v>45974</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18370,7 +18376,7 @@
         <v>45975</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18448,7 +18454,7 @@
         <v>45974</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18541,7 +18547,7 @@
         <v>46106</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18614,7 +18620,7 @@
         <v>46106</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18692,7 +18698,7 @@
         <v>46106</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18765,7 +18771,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18838,7 +18844,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18916,7 +18922,7 @@
         <v>45280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18989,7 +18995,7 @@
         <v>46112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19062,7 +19068,7 @@
         <v>45987</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19135,7 +19141,7 @@
         <v>45821</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19208,7 +19214,7 @@
         <v>45986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19286,7 +19292,7 @@
         <v>45987</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19364,7 +19370,7 @@
         <v>45986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19442,7 +19448,7 @@
         <v>45979</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19515,7 +19521,7 @@
         <v>45505</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19588,7 +19594,7 @@
         <v>44967</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19661,7 +19667,7 @@
         <v>46122</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19734,7 +19740,7 @@
         <v>46122</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19807,7 +19813,7 @@
         <v>45992</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19880,7 +19886,7 @@
         <v>44895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19958,7 +19964,7 @@
         <v>46122</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20031,7 +20037,7 @@
         <v>46122</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20104,7 +20110,7 @@
         <v>45992</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20177,7 +20183,7 @@
         <v>45992</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20255,7 +20261,7 @@
         <v>45992</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20328,7 +20334,7 @@
         <v>45992</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20401,7 +20407,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20474,7 +20480,7 @@
         <v>45827</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20552,7 +20558,7 @@
         <v>45554</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20625,7 +20631,7 @@
         <v>46132</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20698,7 +20704,7 @@
         <v>45833</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20771,7 +20777,7 @@
         <v>45280</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20844,7 +20850,7 @@
         <v>45434</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20917,7 +20923,7 @@
         <v>44494</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20990,7 +20996,7 @@
         <v>45938</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21068,7 +21074,7 @@
         <v>45904</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21146,7 +21152,7 @@
         <v>44949</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21219,7 +21225,7 @@
         <v>45709</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21292,7 +21298,7 @@
         <v>45580</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21365,7 +21371,7 @@
         <v>45709</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21438,7 +21444,7 @@
         <v>45989</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21511,7 +21517,7 @@
         <v>44942</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21584,7 +21590,7 @@
         <v>45365</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21657,7 +21663,7 @@
         <v>45250</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21730,7 +21736,7 @@
         <v>45334</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21803,7 +21809,7 @@
         <v>45953</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21881,7 +21887,7 @@
         <v>44741</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21954,7 +21960,7 @@
         <v>45874</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22027,7 +22033,7 @@
         <v>45642</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22100,7 +22106,7 @@
         <v>45869</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22173,7 +22179,7 @@
         <v>45579</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22251,7 +22257,7 @@
         <v>45735</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22324,7 +22330,7 @@
         <v>45678</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22397,7 +22403,7 @@
         <v>45607</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22475,7 +22481,7 @@
         <v>45691</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22548,7 +22554,7 @@
         <v>45167</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22621,7 +22627,7 @@
         <v>46147</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22699,7 +22705,7 @@
         <v>44617</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22772,7 +22778,7 @@
         <v>45078</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22845,7 +22851,7 @@
         <v>46148</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22923,7 +22929,7 @@
         <v>45831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22996,7 +23002,7 @@
         <v>46153</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23074,7 +23080,7 @@
         <v>46150</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23152,7 +23158,7 @@
         <v>46153</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23230,7 +23236,7 @@
         <v>46150</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23303,7 +23309,7 @@
         <v>46150</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23376,7 +23382,7 @@
         <v>46150</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23454,7 +23460,7 @@
         <v>44895</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23532,7 +23538,7 @@
         <v>45068</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23605,7 +23611,7 @@
         <v>46154</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23683,7 +23689,7 @@
         <v>44910</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23756,7 +23762,7 @@
         <v>44942</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23829,7 +23835,7 @@
         <v>45224</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23907,7 +23913,7 @@
         <v>46160</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23980,7 +23986,7 @@
         <v>45194</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24053,7 +24059,7 @@
         <v>45874</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24131,7 +24137,7 @@
         <v>46160</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24204,7 +24210,7 @@
         <v>46160</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24277,7 +24283,7 @@
         <v>44617</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24350,7 +24356,7 @@
         <v>46160</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24423,7 +24429,7 @@
         <v>46160</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24496,7 +24502,7 @@
         <v>45044</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24569,7 +24575,7 @@
         <v>46163</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24647,7 +24653,7 @@
         <v>46164</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24725,7 +24731,7 @@
         <v>45772</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24798,7 +24804,7 @@
         <v>45708</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24876,7 +24882,7 @@
         <v>45271</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24954,7 +24960,7 @@
         <v>44918</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25027,7 +25033,7 @@
         <v>44918</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25100,7 +25106,7 @@
         <v>45232</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25173,7 +25179,7 @@
         <v>46176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25251,7 +25257,7 @@
         <v>45885</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25324,7 +25330,7 @@
         <v>46177</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25402,7 +25408,7 @@
         <v>45583</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25480,7 +25486,7 @@
         <v>46182</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25553,7 +25559,7 @@
         <v>45548</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25631,7 +25637,7 @@
         <v>46183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25709,7 +25715,7 @@
         <v>44985</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25782,7 +25788,7 @@
         <v>45639</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25860,7 +25866,7 @@
         <v>46185</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25938,7 +25944,7 @@
         <v>45337</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26016,7 +26022,7 @@
         <v>46189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26094,7 +26100,7 @@
         <v>45302</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26167,7 +26173,7 @@
         <v>46191</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26240,7 +26246,7 @@
         <v>46191</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26313,7 +26319,7 @@
         <v>46191</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26386,7 +26392,7 @@
         <v>46191</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26459,7 +26465,7 @@
         <v>46196</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26532,7 +26538,7 @@
         <v>44872</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26605,7 +26611,7 @@
         <v>46198</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26678,7 +26684,7 @@
         <v>45632</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26751,7 +26757,7 @@
         <v>46197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26829,7 +26835,7 @@
         <v>46197</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26902,7 +26908,7 @@
         <v>46197</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26975,7 +26981,7 @@
         <v>46197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27048,7 +27054,7 @@
         <v>46198</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27121,7 +27127,7 @@
         <v>46197</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27199,7 +27205,7 @@
         <v>46202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27272,7 +27278,7 @@
         <v>46202</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27345,7 +27351,7 @@
         <v>46202</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27418,7 +27424,7 @@
         <v>46199</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27496,7 +27502,7 @@
         <v>46203</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27574,7 +27580,7 @@
         <v>46204</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27647,7 +27653,7 @@
         <v>45548</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27725,7 +27731,7 @@
         <v>45365</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27798,7 +27804,7 @@
         <v>45305</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27871,7 +27877,7 @@
         <v>46213</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27949,7 +27955,7 @@
         <v>44580</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28022,7 +28028,7 @@
         <v>44873</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28095,7 +28101,7 @@
         <v>44847</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28168,7 +28174,7 @@
         <v>45344</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28241,7 +28247,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28314,7 +28320,7 @@
         <v>45470</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28392,7 +28398,7 @@
         <v>45565</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28470,7 +28476,7 @@
         <v>45565</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28548,7 +28554,7 @@
         <v>46267</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28626,7 +28632,7 @@
         <v>45463</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28699,7 +28705,7 @@
         <v>46267</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28777,7 +28783,7 @@
         <v>45992</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28850,7 +28856,7 @@
         <v>46191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28923,7 +28929,7 @@
         <v>46230</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28996,7 +29002,7 @@
         <v>46272</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29069,7 +29075,7 @@
         <v>46279</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29142,7 +29148,7 @@
         <v>45098</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29215,7 +29221,7 @@
         <v>46239</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29288,7 +29294,7 @@
         <v>45296</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29361,7 +29367,7 @@
         <v>46283</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29434,7 +29440,7 @@
         <v>44952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29507,7 +29513,7 @@
         <v>45552</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29580,7 +29586,7 @@
         <v>44491</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29653,7 +29659,7 @@
         <v>46198</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29726,7 +29732,7 @@
         <v>45511</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29799,7 +29805,7 @@
         <v>45278</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29872,7 +29878,7 @@
         <v>46126</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29945,7 +29951,7 @@
         <v>45632</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30018,7 +30024,7 @@
         <v>44994</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30091,7 +30097,7 @@
         <v>45477</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30169,7 +30175,7 @@
         <v>45642</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30242,7 +30248,7 @@
         <v>46246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30320,7 +30326,7 @@
         <v>45114</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30393,7 +30399,7 @@
         <v>45484</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30471,7 +30477,7 @@
         <v>46245</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30544,7 +30550,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30622,7 +30628,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30695,7 +30701,7 @@
         <v>46246</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30768,7 +30774,7 @@
         <v>45252</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30841,7 +30847,7 @@
         <v>44943</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30919,7 +30925,7 @@
         <v>44810</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30997,7 +31003,7 @@
         <v>44873</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31070,7 +31076,7 @@
         <v>45282</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31148,7 +31154,7 @@
         <v>44823</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31226,7 +31232,7 @@
         <v>45334</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31299,7 +31305,7 @@
         <v>44790</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31372,7 +31378,7 @@
         <v>46254</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31450,7 +31456,7 @@
         <v>45603</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31523,7 +31529,7 @@
         <v>45406</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31596,7 +31602,7 @@
         <v>46296</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31669,7 +31675,7 @@
         <v>46246</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31742,7 +31748,7 @@
         <v>45251</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31815,7 +31821,7 @@
         <v>46254</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31893,7 +31899,7 @@
         <v>46150</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31971,7 +31977,7 @@
         <v>45162</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32044,7 +32050,7 @@
         <v>45494</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32122,7 +32128,7 @@
         <v>45246</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32195,7 +32201,7 @@
         <v>44896</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32268,7 +32274,7 @@
         <v>45266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32341,7 +32347,7 @@
         <v>45688</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32414,7 +32420,7 @@
         <v>45016</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32487,7 +32493,7 @@
         <v>44617</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32560,7 +32566,7 @@
         <v>44617</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32633,7 +32639,7 @@
         <v>45334</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32706,7 +32712,7 @@
         <v>45495</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32784,7 +32790,7 @@
         <v>45216</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32857,7 +32863,7 @@
         <v>45194</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32930,7 +32936,7 @@
         <v>45448</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33003,7 +33009,7 @@
         <v>45644</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33076,7 +33082,7 @@
         <v>45434</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33149,7 +33155,7 @@
         <v>45772</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33222,7 +33228,7 @@
         <v>45784</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33300,7 +33306,7 @@
         <v>45601</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33373,7 +33379,7 @@
         <v>45478</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33446,7 +33452,7 @@
         <v>44945</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33524,7 +33530,7 @@
         <v>45686</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33597,7 +33603,7 @@
         <v>45792</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33675,7 +33681,7 @@
         <v>45436</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33748,7 +33754,7 @@
         <v>45961</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33826,7 +33832,7 @@
         <v>45961</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33904,7 +33910,7 @@
         <v>45961</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33982,7 +33988,7 @@
         <v>45960</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34060,7 +34066,7 @@
         <v>46070</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34133,7 +34139,7 @@
         <v>46168</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34206,7 +34212,7 @@
         <v>46178</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34279,7 +34285,7 @@
         <v>46178</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34352,7 +34358,7 @@
         <v>46181</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34430,7 +34436,7 @@
         <v>46185</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45947</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44969</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46297</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>45425</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>45789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45554</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46178</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45940</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45775</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45470</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>45944</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46297</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45960</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>46105</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4579,75 +4579,303 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
+          <t>A 36786-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Orange taggsvamp
+Rynkskinn
+Talltagel
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 36786-2026 artfynd.xlsx", "A 36786-2026")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 36786-2026 karta.png", "A 36786-2026")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 36786-2026 georefererad karta.tif", "A 36786-2026")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 36786-2026 FSC-klagomål.docx", "A 36786-2026")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 36786-2026 FSC-klagomål mail.docx", "A 36786-2026")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 36786-2026 tillsynsbegäran.docx", "A 36786-2026")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 36786-2026 tillsynsbegäran mail.docx", "A 36786-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 36806-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>7</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Orange taggsvamp
+Rynkskinn
+Talltagel
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 36806-2026 artfynd.xlsx", "A 36806-2026")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 36806-2026 karta.png", "A 36806-2026")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 36806-2026 georefererad karta.tif", "A 36806-2026")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 36806-2026 FSC-klagomål.docx", "A 36806-2026")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 36806-2026 FSC-klagomål mail.docx", "A 36806-2026")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 36806-2026 tillsynsbegäran.docx", "A 36806-2026")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 36806-2026 tillsynsbegäran mail.docx", "A 36806-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>A 73616-2021</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
         <v>44552</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="E36" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>7.3</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M36" t="n">
         <v>2</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R36" t="n">
         <v>2</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S36" t="n">
         <v>4</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T36" t="n">
         <v>8</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U36" t="n">
         <v>8</v>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Sprickporing
@@ -4655,120 +4883,120 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 73616-2021 artfynd.xlsx", "A 73616-2021")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 73616-2021 karta.png", "A 73616-2021")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 73616-2021 georefererad karta.tif", "A 73616-2021")</f>
         <v/>
       </c>
-      <c r="Z34">
+      <c r="Z36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/knärot/A 73616-2021 karta knärot.png", "A 73616-2021")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 73616-2021 FSC-klagomål.docx", "A 73616-2021")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 73616-2021 FSC-klagomål mail.docx", "A 73616-2021")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 73616-2021 tillsynsbegäran.docx", "A 73616-2021")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 73616-2021 tillsynsbegäran mail.docx", "A 73616-2021")</f>
         <v/>
       </c>
-      <c r="AE34">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/fåglar/A 73616-2021 prioriterade fågelarter.docx", "A 73616-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>A 28582-2025</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
         <v>45819</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="E37" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I37" t="n">
         <v>26.1</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L37" t="n">
         <v>3</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>3</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>4</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U37" t="n">
         <v>5</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Kolflarnlav
@@ -4776,112 +5004,112 @@
 Plattlummer</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 28582-2025 artfynd.xlsx", "A 28582-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 28582-2025 karta.png", "A 28582-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 28582-2025 georefererad karta.tif", "A 28582-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 28582-2025 FSC-klagomål.docx", "A 28582-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 28582-2025 FSC-klagomål mail.docx", "A 28582-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 28582-2025 tillsynsbegäran.docx", "A 28582-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 28582-2025 tillsynsbegäran mail.docx", "A 28582-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>A 23807-2026</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="E38" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I38" t="n">
         <v>0.9</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>2</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>2</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R38" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S38" t="n">
         <v>4</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T38" t="n">
         <v>5</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Ulltickeporing
 Rosenticka
@@ -4889,112 +5117,112 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 23807-2026 artfynd.xlsx", "A 23807-2026")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 23807-2026 karta.png", "A 23807-2026")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 23807-2026 georefererad karta.tif", "A 23807-2026")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 23807-2026 FSC-klagomål.docx", "A 23807-2026")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 23807-2026 FSC-klagomål mail.docx", "A 23807-2026")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 23807-2026 tillsynsbegäran.docx", "A 23807-2026")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 23807-2026 tillsynsbegäran mail.docx", "A 23807-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>A 53641-2025</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="E37" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="E39" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I39" t="n">
         <v>4.7</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>4</v>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>4</v>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>4</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T39" t="n">
         <v>5</v>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Motaggsvamp
@@ -5002,112 +5230,112 @@
 Skarp dropptaggsvamp</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 53641-2025 artfynd.xlsx", "A 53641-2025")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 53641-2025 karta.png", "A 53641-2025")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 53641-2025 georefererad karta.tif", "A 53641-2025")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 53641-2025 FSC-klagomål.docx", "A 53641-2025")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 53641-2025 FSC-klagomål mail.docx", "A 53641-2025")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 53641-2025 tillsynsbegäran.docx", "A 53641-2025")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 53641-2025 tillsynsbegäran mail.docx", "A 53641-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>A 30592-2026</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="E40" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="I40" t="n">
         <v>10</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>2</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S40" t="n">
         <v>4</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T40" t="n">
         <v>5</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U40" t="n">
         <v>5</v>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Kolflarnlav
@@ -5115,112 +5343,112 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 30592-2026 artfynd.xlsx", "A 30592-2026")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 30592-2026 karta.png", "A 30592-2026")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 30592-2026 georefererad karta.tif", "A 30592-2026")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 30592-2026 FSC-klagomål.docx", "A 30592-2026")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 30592-2026 FSC-klagomål mail.docx", "A 30592-2026")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 30592-2026 tillsynsbegäran.docx", "A 30592-2026")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 30592-2026 tillsynsbegäran mail.docx", "A 30592-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>A 30723-2026</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="E39" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="E41" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="I41" t="n">
         <v>4.5</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J41" t="n">
         <v>2</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M41" t="n">
         <v>2</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>3</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R41" t="n">
         <v>2</v>
       </c>
-      <c r="S39" t="n">
+      <c r="S41" t="n">
         <v>4</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T41" t="n">
         <v>5</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U41" t="n">
         <v>1</v>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Garnlav
@@ -5228,112 +5456,112 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 30723-2026 artfynd.xlsx", "A 30723-2026")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 30723-2026 karta.png", "A 30723-2026")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 30723-2026 georefererad karta.tif", "A 30723-2026")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 30723-2026 FSC-klagomål.docx", "A 30723-2026")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 30723-2026 FSC-klagomål mail.docx", "A 30723-2026")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 30723-2026 tillsynsbegäran.docx", "A 30723-2026")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 30723-2026 tillsynsbegäran mail.docx", "A 30723-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>A 35214-2026</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
         <v>46260</v>
       </c>
-      <c r="E40" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="E42" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ÄLVSBYN</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="I42" t="n">
         <v>1.7</v>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L42" t="n">
         <v>3</v>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
         <v>3</v>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
         <v>4</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T42" t="n">
         <v>5</v>
       </c>
-      <c r="U40" t="n">
+      <c r="U42" t="n">
         <v>4</v>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Blå taggsvamp
 Mörk kolflarnlav
@@ -5341,258 +5569,32 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W40">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 35214-2026 artfynd.xlsx", "A 35214-2026")</f>
         <v/>
       </c>
-      <c r="X40">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 35214-2026 karta.png", "A 35214-2026")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 35214-2026 georefererad karta.tif", "A 35214-2026")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 35214-2026 FSC-klagomål.docx", "A 35214-2026")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 35214-2026 FSC-klagomål mail.docx", "A 35214-2026")</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 35214-2026 tillsynsbegäran.docx", "A 35214-2026")</f>
         <v/>
       </c>
-      <c r="AD40">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 35214-2026 tillsynsbegäran mail.docx", "A 35214-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>A 36786-2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>3</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>5</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Orange taggsvamp
-Rynkskinn
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 36786-2026 artfynd.xlsx", "A 36786-2026")</f>
-        <v/>
-      </c>
-      <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 36786-2026 karta.png", "A 36786-2026")</f>
-        <v/>
-      </c>
-      <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 36786-2026 georefererad karta.tif", "A 36786-2026")</f>
-        <v/>
-      </c>
-      <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 36786-2026 FSC-klagomål.docx", "A 36786-2026")</f>
-        <v/>
-      </c>
-      <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 36786-2026 FSC-klagomål mail.docx", "A 36786-2026")</f>
-        <v/>
-      </c>
-      <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 36786-2026 tillsynsbegäran.docx", "A 36786-2026")</f>
-        <v/>
-      </c>
-      <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 36786-2026 tillsynsbegäran mail.docx", "A 36786-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A 36806-2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ÄLVSBYN</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>5</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Orange taggsvamp
-Rynkskinn
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/artfynd/A 36806-2026 artfynd.xlsx", "A 36806-2026")</f>
-        <v/>
-      </c>
-      <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor/A 36806-2026 karta.png", "A 36806-2026")</f>
-        <v/>
-      </c>
-      <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/kartor_geotiff/A 36806-2026 georefererad karta.tif", "A 36806-2026")</f>
-        <v/>
-      </c>
-      <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomål/A 36806-2026 FSC-klagomål.docx", "A 36806-2026")</f>
-        <v/>
-      </c>
-      <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/klagomålsmail/A 36806-2026 FSC-klagomål mail.docx", "A 36806-2026")</f>
-        <v/>
-      </c>
-      <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsyn/A 36806-2026 tillsynsbegäran.docx", "A 36806-2026")</f>
-        <v/>
-      </c>
-      <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2560/tillsynsmail/A 36806-2026 tillsynsbegäran mail.docx", "A 36806-2026")</f>
         <v/>
       </c>
     </row>
@@ -5616,7 +5618,7 @@
         <v>45789</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5728,7 +5730,7 @@
         <v>45576</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5840,7 +5842,7 @@
         <v>45846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5952,7 +5954,7 @@
         <v>45600</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6064,7 +6066,7 @@
         <v>46195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6176,7 +6178,7 @@
         <v>46206</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6288,7 +6290,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6395,7 +6397,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6502,7 +6504,7 @@
         <v>46211</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6614,7 +6616,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6726,7 +6728,7 @@
         <v>44671</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6837,7 +6839,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6948,7 +6950,7 @@
         <v>45407</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7059,7 +7061,7 @@
         <v>45944</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7170,7 +7172,7 @@
         <v>45980</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7281,7 +7283,7 @@
         <v>45621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7392,7 +7394,7 @@
         <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7503,7 +7505,7 @@
         <v>45574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7614,7 +7616,7 @@
         <v>45516</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7725,7 +7727,7 @@
         <v>45450</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7836,7 +7838,7 @@
         <v>46195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7947,7 +7949,7 @@
         <v>45576</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8053,7 +8055,7 @@
         <v>45028</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8164,7 +8166,7 @@
         <v>44813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8274,7 +8276,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8388,7 +8390,7 @@
         <v>45922</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8493,7 +8495,7 @@
         <v>45938</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8598,7 +8600,7 @@
         <v>45944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8708,7 +8710,7 @@
         <v>45953</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8818,7 +8820,7 @@
         <v>45957</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8928,7 +8930,7 @@
         <v>45960</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9038,7 +9040,7 @@
         <v>45953</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9148,7 +9150,7 @@
         <v>45989</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9258,7 +9260,7 @@
         <v>45993</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9368,7 +9370,7 @@
         <v>45840</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9482,7 +9484,7 @@
         <v>45847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9592,7 +9594,7 @@
         <v>45565</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9697,7 +9699,7 @@
         <v>45623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9807,7 +9809,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9917,7 +9919,7 @@
         <v>45629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10022,7 +10024,7 @@
         <v>46147</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10132,7 +10134,7 @@
         <v>46147</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10242,7 +10244,7 @@
         <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10352,7 +10354,7 @@
         <v>46164</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10462,7 +10464,7 @@
         <v>46184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10572,7 +10574,7 @@
         <v>46197</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10682,7 +10684,7 @@
         <v>46197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10791,7 +10793,7 @@
         <v>46197</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10900,7 +10902,7 @@
         <v>44832</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11010,7 +11012,7 @@
         <v>46261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11120,7 +11122,7 @@
         <v>46267</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11230,7 +11232,7 @@
         <v>45793</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11340,7 +11342,7 @@
         <v>46297</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11450,7 +11452,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11528,7 +11530,7 @@
         <v>44868</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11601,7 +11603,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11674,7 +11676,7 @@
         <v>44491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11752,7 +11754,7 @@
         <v>44491</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11830,7 +11832,7 @@
         <v>44522</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11903,7 +11905,7 @@
         <v>44552</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11976,7 +11978,7 @@
         <v>44484</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12049,7 +12051,7 @@
         <v>44847</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12122,7 +12124,7 @@
         <v>44825</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12195,7 +12197,7 @@
         <v>44741</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12268,7 +12270,7 @@
         <v>44750</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12341,7 +12343,7 @@
         <v>44602</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12414,7 +12416,7 @@
         <v>44515</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12487,7 +12489,7 @@
         <v>44819</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12560,7 +12562,7 @@
         <v>44795</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12633,7 +12635,7 @@
         <v>44813</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12711,7 +12713,7 @@
         <v>44476</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12784,7 +12786,7 @@
         <v>45554</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12857,7 +12859,7 @@
         <v>45078</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12930,7 +12932,7 @@
         <v>45622</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13008,7 +13010,7 @@
         <v>44677</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13081,7 +13083,7 @@
         <v>44959</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13154,7 +13156,7 @@
         <v>44732</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13227,7 +13229,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13300,7 +13302,7 @@
         <v>45478</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13373,7 +13375,7 @@
         <v>45961</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13451,7 +13453,7 @@
         <v>45629</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13524,7 +13526,7 @@
         <v>45583</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13602,7 +13604,7 @@
         <v>44728</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13675,7 +13677,7 @@
         <v>45791</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13748,7 +13750,7 @@
         <v>45933</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13821,7 +13823,7 @@
         <v>46019</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13894,7 +13896,7 @@
         <v>46019</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13967,7 +13969,7 @@
         <v>46019</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14040,7 +14042,7 @@
         <v>45688</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14113,7 +14115,7 @@
         <v>45895</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14191,7 +14193,7 @@
         <v>45896</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14269,7 +14271,7 @@
         <v>45896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14347,7 +14349,7 @@
         <v>44855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14420,7 +14422,7 @@
         <v>45792</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14498,7 +14500,7 @@
         <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14576,7 +14578,7 @@
         <v>45016</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14649,7 +14651,7 @@
         <v>45525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14727,7 +14729,7 @@
         <v>45916</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14800,7 +14802,7 @@
         <v>45916</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14873,7 +14875,7 @@
         <v>46050</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14951,7 +14953,7 @@
         <v>45919</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15024,7 +15026,7 @@
         <v>45803</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15097,7 +15099,7 @@
         <v>45919</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15170,7 +15172,7 @@
         <v>45782</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15243,7 +15245,7 @@
         <v>45552</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15321,7 +15323,7 @@
         <v>45804</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15399,7 +15401,7 @@
         <v>45805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15477,7 +15479,7 @@
         <v>46055</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15550,7 +15552,7 @@
         <v>45925</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15623,7 +15625,7 @@
         <v>45925</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15696,7 +15698,7 @@
         <v>45929</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15774,7 +15776,7 @@
         <v>45931</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15852,7 +15854,7 @@
         <v>45932</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15930,7 +15932,7 @@
         <v>45933</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16008,7 +16010,7 @@
         <v>45936</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16081,7 +16083,7 @@
         <v>45808</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16159,7 +16161,7 @@
         <v>44552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16237,7 +16239,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16310,7 +16312,7 @@
         <v>45938</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16388,7 +16390,7 @@
         <v>45220</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16466,7 +16468,7 @@
         <v>45945</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16539,7 +16541,7 @@
         <v>45947</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16617,7 +16619,7 @@
         <v>45946</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16690,7 +16692,7 @@
         <v>45950</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16763,7 +16765,7 @@
         <v>45812</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16836,7 +16838,7 @@
         <v>44851</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16909,7 +16911,7 @@
         <v>45957</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16987,7 +16989,7 @@
         <v>45576</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17060,7 +17062,7 @@
         <v>45222</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17133,7 +17135,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17211,7 +17213,7 @@
         <v>45961</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17289,7 +17291,7 @@
         <v>45961</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17367,7 +17369,7 @@
         <v>45960</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17445,7 +17447,7 @@
         <v>45964</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17518,7 +17520,7 @@
         <v>45561</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17596,7 +17598,7 @@
         <v>45561</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17669,7 +17671,7 @@
         <v>45125</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17742,7 +17744,7 @@
         <v>45220</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17820,7 +17822,7 @@
         <v>45972</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17898,7 +17900,7 @@
         <v>45973</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17976,7 +17978,7 @@
         <v>45511</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18049,7 +18051,7 @@
         <v>45972</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18127,7 +18129,7 @@
         <v>45265</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18205,7 +18207,7 @@
         <v>45975</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18283,7 +18285,7 @@
         <v>45974</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18376,7 +18378,7 @@
         <v>45975</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18454,7 +18456,7 @@
         <v>45974</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18547,7 +18549,7 @@
         <v>46106</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18620,7 +18622,7 @@
         <v>46106</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18698,7 +18700,7 @@
         <v>46106</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18771,7 +18773,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18844,7 +18846,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18922,7 +18924,7 @@
         <v>45280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18995,7 +18997,7 @@
         <v>46112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19068,7 +19070,7 @@
         <v>45987</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19141,7 +19143,7 @@
         <v>45821</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19214,7 +19216,7 @@
         <v>45986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19292,7 +19294,7 @@
         <v>45987</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19370,7 +19372,7 @@
         <v>45986</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19448,7 +19450,7 @@
         <v>45979</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19521,7 +19523,7 @@
         <v>45505</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19594,7 +19596,7 @@
         <v>44967</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19667,7 +19669,7 @@
         <v>46122</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19740,7 +19742,7 @@
         <v>46122</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19813,7 +19815,7 @@
         <v>45992</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19886,7 +19888,7 @@
         <v>44895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19964,7 +19966,7 @@
         <v>46122</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20037,7 +20039,7 @@
         <v>46122</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20110,7 +20112,7 @@
         <v>45992</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20183,7 +20185,7 @@
         <v>45992</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20261,7 +20263,7 @@
         <v>45992</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20334,7 +20336,7 @@
         <v>45992</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20407,7 +20409,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20480,7 +20482,7 @@
         <v>45827</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20558,7 +20560,7 @@
         <v>45554</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20631,7 +20633,7 @@
         <v>46132</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20704,7 +20706,7 @@
         <v>45833</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20777,7 +20779,7 @@
         <v>45280</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20850,7 +20852,7 @@
         <v>45434</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20923,7 +20925,7 @@
         <v>44494</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20996,7 +20998,7 @@
         <v>45938</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21074,7 +21076,7 @@
         <v>45904</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21152,7 +21154,7 @@
         <v>44949</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21225,7 +21227,7 @@
         <v>45709</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21298,7 +21300,7 @@
         <v>45580</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21371,7 +21373,7 @@
         <v>45709</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21444,7 +21446,7 @@
         <v>45989</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21517,7 +21519,7 @@
         <v>44942</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21590,7 +21592,7 @@
         <v>45365</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21663,7 +21665,7 @@
         <v>45250</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21736,7 +21738,7 @@
         <v>45334</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21809,7 +21811,7 @@
         <v>45953</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21887,7 +21889,7 @@
         <v>44741</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21960,7 +21962,7 @@
         <v>45874</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22033,7 +22035,7 @@
         <v>45642</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22106,7 +22108,7 @@
         <v>45869</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22179,7 +22181,7 @@
         <v>45579</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22257,7 +22259,7 @@
         <v>45735</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22330,7 +22332,7 @@
         <v>45678</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22403,7 +22405,7 @@
         <v>45607</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22481,7 +22483,7 @@
         <v>45691</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22554,7 +22556,7 @@
         <v>45167</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22627,7 +22629,7 @@
         <v>46147</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22705,7 +22707,7 @@
         <v>44617</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22778,7 +22780,7 @@
         <v>45078</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22851,7 +22853,7 @@
         <v>46148</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22929,7 +22931,7 @@
         <v>45831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23002,7 +23004,7 @@
         <v>46153</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23080,7 +23082,7 @@
         <v>46150</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23158,7 +23160,7 @@
         <v>46153</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23236,7 +23238,7 @@
         <v>46150</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23309,7 +23311,7 @@
         <v>46150</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23382,7 +23384,7 @@
         <v>46150</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23460,7 +23462,7 @@
         <v>44895</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23538,7 +23540,7 @@
         <v>45068</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23611,7 +23613,7 @@
         <v>46154</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23689,7 +23691,7 @@
         <v>44910</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23762,7 +23764,7 @@
         <v>44942</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23835,7 +23837,7 @@
         <v>45224</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23913,7 +23915,7 @@
         <v>46160</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23986,7 +23988,7 @@
         <v>45194</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24059,7 +24061,7 @@
         <v>45874</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24137,7 +24139,7 @@
         <v>46160</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24210,7 +24212,7 @@
         <v>46160</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24283,7 +24285,7 @@
         <v>44617</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24356,7 +24358,7 @@
         <v>46160</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24429,7 +24431,7 @@
         <v>46160</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24502,7 +24504,7 @@
         <v>45044</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24575,7 +24577,7 @@
         <v>46163</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24653,7 +24655,7 @@
         <v>46164</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24731,7 +24733,7 @@
         <v>45772</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24804,7 +24806,7 @@
         <v>45708</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24882,7 +24884,7 @@
         <v>45271</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24960,7 +24962,7 @@
         <v>44918</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25033,7 +25035,7 @@
         <v>44918</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25106,7 +25108,7 @@
         <v>45232</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25179,7 +25181,7 @@
         <v>46176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25257,7 +25259,7 @@
         <v>45885</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25330,7 +25332,7 @@
         <v>46177</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25408,7 +25410,7 @@
         <v>45583</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25486,7 +25488,7 @@
         <v>46182</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25559,7 +25561,7 @@
         <v>45548</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25637,7 +25639,7 @@
         <v>46183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25715,7 +25717,7 @@
         <v>44985</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25788,7 +25790,7 @@
         <v>45639</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25866,7 +25868,7 @@
         <v>46185</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25944,7 +25946,7 @@
         <v>45337</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26022,7 +26024,7 @@
         <v>46189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26100,7 +26102,7 @@
         <v>45302</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26173,7 +26175,7 @@
         <v>46191</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26246,7 +26248,7 @@
         <v>46191</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26319,7 +26321,7 @@
         <v>46191</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26392,7 +26394,7 @@
         <v>46191</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26465,7 +26467,7 @@
         <v>46196</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26538,7 +26540,7 @@
         <v>44872</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26611,7 +26613,7 @@
         <v>46198</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26684,7 +26686,7 @@
         <v>45632</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26757,7 +26759,7 @@
         <v>46197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26835,7 +26837,7 @@
         <v>46197</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26908,7 +26910,7 @@
         <v>46197</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26981,7 +26983,7 @@
         <v>46197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27054,7 +27056,7 @@
         <v>46198</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27127,7 +27129,7 @@
         <v>46197</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27205,7 +27207,7 @@
         <v>46202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27278,7 +27280,7 @@
         <v>46202</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27351,7 +27353,7 @@
         <v>46202</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27424,7 +27426,7 @@
         <v>46199</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27502,7 +27504,7 @@
         <v>46203</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27580,7 +27582,7 @@
         <v>46204</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27653,7 +27655,7 @@
         <v>45548</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27731,7 +27733,7 @@
         <v>45365</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27804,7 +27806,7 @@
         <v>45305</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27877,7 +27879,7 @@
         <v>46213</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27955,7 +27957,7 @@
         <v>44580</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28028,7 +28030,7 @@
         <v>44873</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28101,7 +28103,7 @@
         <v>44847</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28174,7 +28176,7 @@
         <v>45344</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28247,7 +28249,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28320,7 +28322,7 @@
         <v>45470</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28398,7 +28400,7 @@
         <v>45565</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28476,7 +28478,7 @@
         <v>45565</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28554,7 +28556,7 @@
         <v>46267</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28632,7 +28634,7 @@
         <v>45463</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28705,7 +28707,7 @@
         <v>46267</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28783,7 +28785,7 @@
         <v>45992</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28856,7 +28858,7 @@
         <v>46191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28929,7 +28931,7 @@
         <v>46230</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29002,7 +29004,7 @@
         <v>46272</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29075,7 +29077,7 @@
         <v>46279</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29148,7 +29150,7 @@
         <v>45098</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29221,7 +29223,7 @@
         <v>46239</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29294,7 +29296,7 @@
         <v>45296</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29367,7 +29369,7 @@
         <v>46283</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29440,7 +29442,7 @@
         <v>44952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29513,7 +29515,7 @@
         <v>45552</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29586,7 +29588,7 @@
         <v>44491</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29659,7 +29661,7 @@
         <v>46198</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29732,7 +29734,7 @@
         <v>45511</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29805,7 +29807,7 @@
         <v>45278</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29878,7 +29880,7 @@
         <v>46126</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29951,7 +29953,7 @@
         <v>45632</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30024,7 +30026,7 @@
         <v>44994</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30097,7 +30099,7 @@
         <v>45477</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30175,7 +30177,7 @@
         <v>45642</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30248,7 +30250,7 @@
         <v>46246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30326,7 +30328,7 @@
         <v>45114</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30399,7 +30401,7 @@
         <v>45484</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30477,7 +30479,7 @@
         <v>46245</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30550,7 +30552,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30628,7 +30630,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30701,7 +30703,7 @@
         <v>46246</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30774,7 +30776,7 @@
         <v>45252</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30847,7 +30849,7 @@
         <v>44943</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30925,7 +30927,7 @@
         <v>44810</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31003,7 +31005,7 @@
         <v>44873</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31076,7 +31078,7 @@
         <v>45282</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31154,7 +31156,7 @@
         <v>44823</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31232,7 +31234,7 @@
         <v>45334</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31305,7 +31307,7 @@
         <v>44790</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31378,7 +31380,7 @@
         <v>46254</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31456,7 +31458,7 @@
         <v>45603</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31529,7 +31531,7 @@
         <v>45406</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31602,7 +31604,7 @@
         <v>46296</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31675,7 +31677,7 @@
         <v>46246</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31748,7 +31750,7 @@
         <v>45251</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31821,7 +31823,7 @@
         <v>46254</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31899,7 +31901,7 @@
         <v>46150</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31977,7 +31979,7 @@
         <v>45162</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32050,7 +32052,7 @@
         <v>45494</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32128,7 +32130,7 @@
         <v>45246</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32201,7 +32203,7 @@
         <v>44896</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32274,7 +32276,7 @@
         <v>45266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32347,7 +32349,7 @@
         <v>45688</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32420,7 +32422,7 @@
         <v>45016</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32493,7 +32495,7 @@
         <v>44617</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32566,7 +32568,7 @@
         <v>44617</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32639,7 +32641,7 @@
         <v>45334</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32712,7 +32714,7 @@
         <v>45495</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32790,7 +32792,7 @@
         <v>45216</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32863,7 +32865,7 @@
         <v>45194</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32936,7 +32938,7 @@
         <v>45448</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33009,7 +33011,7 @@
         <v>45644</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33082,7 +33084,7 @@
         <v>45434</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33155,7 +33157,7 @@
         <v>45772</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33228,7 +33230,7 @@
         <v>45784</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33306,7 +33308,7 @@
         <v>45601</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33379,7 +33381,7 @@
         <v>45478</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33452,7 +33454,7 @@
         <v>44945</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33530,7 +33532,7 @@
         <v>45686</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33603,7 +33605,7 @@
         <v>45792</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33681,7 +33683,7 @@
         <v>45436</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33754,7 +33756,7 @@
         <v>45961</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33832,7 +33834,7 @@
         <v>45961</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33910,7 +33912,7 @@
         <v>45961</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33988,7 +33990,7 @@
         <v>45960</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34066,7 +34068,7 @@
         <v>46070</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34139,7 +34141,7 @@
         <v>46168</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34212,7 +34214,7 @@
         <v>46178</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34285,7 +34287,7 @@
         <v>46178</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34358,7 +34360,7 @@
         <v>46181</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34436,7 +34438,7 @@
         <v>46185</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45947</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44969</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46297</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>45425</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45894</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45789</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45554</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46178</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45940</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45775</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45470</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>45944</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46297</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45573</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>45960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>46105</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>46272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>46272</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45819</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>46164</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46211</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45789</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45576</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45600</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>46206</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>46211</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44671</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45516</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>45407</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45576</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45944</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45450</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45980</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>46164</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>46195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45028</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45922</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44832</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45938</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45953</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>45957</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45960</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>45847</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>45565</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>45629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>45989</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45993</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45922</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46147</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>46147</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>46164</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46184</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>46197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>46197</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>46197</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>46267</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45793</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>46297</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>46261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46304</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44868</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44491</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44491</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>44522</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44484</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>44847</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44825</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44741</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44819</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44750</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44795</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44813</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44602</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44515</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45232</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45365</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45434</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45365</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44918</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45334</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44896</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45334</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45495</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>44873</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45735</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44952</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>45554</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44847</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45548</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44872</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45463</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44617</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45216</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45632</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45576</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>45271</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45220</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45282</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45885</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45629</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45607</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>45477</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>44873</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45580</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>44942</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45265</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45895</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45896</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45896</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45561</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44985</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45579</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>44895</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>45305</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45642</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45280</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45639</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45916</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45772</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45784</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45068</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45511</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45167</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45583</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45478</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45601</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45919</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45919</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45552</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45552</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45510</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44677</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45691</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45925</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45644</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45792</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45565</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45791</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44910</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>44943</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45932</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45337</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>44552</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45252</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45484</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>45931</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45525</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45933</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45936</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45434</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>45344</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45782</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45803</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>44617</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>45804</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45805</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45938</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45194</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45808</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45938</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45220</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45583</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45222</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45812</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44617</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45946</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45945</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45561</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44732</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45950</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45821</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>44851</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45505</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45827</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45194</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44728</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45960</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45960</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45833</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45961</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45961</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45964</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45224</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45511</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45278</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45266</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45162</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45972</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45565</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45972</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45708</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45078</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44790</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45974</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45632</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45642</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45975</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>45280</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45296</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44741</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>45975</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45869</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45874</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45251</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45980</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44855</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45831</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44823</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45016</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44494</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45772</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45016</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45494</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45044</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>44795</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45986</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45986</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44810</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>46106</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>46106</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45987</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45987</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45992</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45992</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45992</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45688</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45406</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45992</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44967</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45302</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>46112</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45979</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>44994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45548</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46122</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>46122</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>46122</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45470</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45961</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45078</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45448</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44942</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45246</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44959</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45709</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>46019</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>46019</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>46019</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45603</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45933</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45688</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45250</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44491</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44617</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45938</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45989</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45960</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45114</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>44949</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45334</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45904</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45874</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45709</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45554</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45125</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>46050</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>46055</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>45678</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>46148</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>46147</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>46150</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46150</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>46150</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>46150</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>46153</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>46154</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46153</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>46160</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>46160</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46160</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>46160</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>46160</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>46163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>46164</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>46177</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>46176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>46183</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>46182</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>46185</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>46189</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>46191</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>46191</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>46197</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>46197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>46197</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>46197</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>46196</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>46197</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>46198</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>46198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>46199</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>46202</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>46203</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>46202</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>46202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>46204</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>46213</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>46196</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46267</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46267</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45992</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46191</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>46230</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>46279</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>46239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>46283</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>46288</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>46126</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>46198</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>46288</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46245</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>46246</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>46246</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>46296</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>46246</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>46254</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>46254</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46150</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>46191</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>46191</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>45478</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>44945</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>45686</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>45792</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>45436</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>45961</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45961</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45961</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>46070</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>46168</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>46178</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>46178</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>46181</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>46185</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45947</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>44969</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46297</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>45425</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45894</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45789</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45554</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46178</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45940</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45775</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45470</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>45944</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46297</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45573</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>45960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>46105</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>46272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>46272</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45819</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>46164</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46211</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45789</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45576</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45600</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>46206</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>46211</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44671</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45516</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>45407</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45576</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45944</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45450</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45980</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>46164</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>46195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45028</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45922</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44832</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45938</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45953</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>45957</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45960</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>45847</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>45565</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>45629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>45989</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45993</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45922</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46147</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>46147</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>46150</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>46164</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46184</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>46197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>46197</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>46197</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>46267</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45793</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>46297</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>46261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>46304</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44868</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44491</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44491</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>44522</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>44484</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>44847</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44825</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44741</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44819</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44750</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44795</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44813</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44602</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44515</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45232</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45365</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45434</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45365</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44918</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45334</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44896</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45334</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>45495</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>44873</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45735</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44952</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>45554</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44847</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45548</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44872</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45463</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44617</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45216</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45632</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45576</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>45271</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45220</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45282</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45885</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45629</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45607</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>45477</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>44873</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45580</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>44942</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45265</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45895</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45896</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45896</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45561</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44985</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45579</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>44895</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>45305</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45642</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45280</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45639</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45916</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45772</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45784</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45068</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45511</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45167</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45583</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45478</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45601</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45919</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45919</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45552</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45552</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45510</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44677</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45691</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45925</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45644</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45792</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45565</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45791</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44910</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>44943</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45932</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45337</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>44552</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45252</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45484</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>45931</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45525</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45933</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45936</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45434</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>45344</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45782</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45803</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>44617</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>45804</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45805</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45938</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45194</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45808</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45938</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45220</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45583</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45222</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45812</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44617</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45946</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45945</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45561</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44732</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45950</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45821</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>44851</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45505</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45827</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45194</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44728</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45960</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45960</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45833</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45961</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45961</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45964</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45224</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45511</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45278</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45266</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45162</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45972</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45565</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45972</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45708</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45078</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44790</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45974</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45632</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45642</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45975</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>45280</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45296</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44741</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>45975</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45869</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45874</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45251</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45980</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44855</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45831</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44823</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45016</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44494</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45772</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45016</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45494</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45044</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>44795</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45986</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45986</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44810</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>46106</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>46106</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45987</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45987</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45992</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45992</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45992</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45688</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45406</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45992</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44967</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45302</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>46112</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45979</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>44994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45548</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46122</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>46122</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>46122</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45470</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45961</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45078</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45448</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44942</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45246</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44959</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45709</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>46019</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>46019</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>46019</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45603</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45933</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45688</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45250</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>44491</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44617</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45938</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45989</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45960</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45114</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>44949</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45334</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45904</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45874</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45709</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45554</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45125</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>46050</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>46055</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>45678</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>46148</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>46147</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>46150</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46150</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>46150</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>46150</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>46153</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>46154</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46153</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>46160</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>46160</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46160</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>46160</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>46160</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>46163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>46164</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>46177</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>46176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>46183</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>46182</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>46185</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>46189</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>46191</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>46191</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>46197</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>46197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>46197</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>46197</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>46196</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>46197</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>46198</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>46198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>46199</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>46202</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>46203</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>46202</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>46202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>46204</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>46213</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>46196</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46267</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46267</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45992</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46191</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>46230</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>46279</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>46239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>46283</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>46288</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>46126</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>46198</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>46288</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46245</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>46246</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>46246</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>46296</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>46246</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>46254</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>46254</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46150</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>46191</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>46191</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>45478</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>44945</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>45686</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>45792</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>45436</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>45961</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45961</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45961</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>46070</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>46168</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>46178</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>46178</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>46181</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>46185</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45947</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44969</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>46297</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45425</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45554</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>46178</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>46288</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>45470</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>45775</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45944</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>46297</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>46105</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>46272</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>46272</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44552</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>46164</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>46211</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>46309</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>46311</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45819</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45576</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>45600</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>46206</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>46211</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>45789</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>45846</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44671</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45407</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45621</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45980</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>46164</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45574</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>45516</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>45450</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>46195</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45576</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>46311</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45028</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44813</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44487</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45922</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>46147</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>46147</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45922</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>45938</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45944</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45623</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45953</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45960</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>46164</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45993</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45953</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>44832</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>46197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>46197</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>46197</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45793</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>46297</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>46261</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>46304</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>46309</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>46267</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45840</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45847</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45629</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44868</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>44552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44491</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44491</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44522</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>44825</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44741</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44750</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>44515</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44819</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>44795</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>44813</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44677</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45554</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>45622</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44959</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44795</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44732</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45583</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44728</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44855</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45016</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45552</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44552</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44851</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45576</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45125</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45561</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45220</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45265</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45511</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45280</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45709</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45989</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>44967</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>44895</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45510</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45885</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45895</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45554</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45896</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45334</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45896</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45953</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45874</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45280</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45434</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44494</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45678</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44949</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45580</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45916</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45916</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45919</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>46147</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>44942</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45925</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45925</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45365</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>46148</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45929</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45931</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>46153</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>46150</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45932</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>46153</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>46150</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>46150</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45933</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46150</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45938</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>45938</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>45945</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46154</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45947</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45642</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45957</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45961</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45961</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45960</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45579</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45735</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>46160</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>46160</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>46160</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45607</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>46160</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>46160</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45691</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>45167</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45972</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45973</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45972</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44617</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45975</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45975</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45078</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46163</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45979</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44895</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45068</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>46164</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44910</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45987</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45986</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45987</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45986</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45224</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45992</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45194</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45992</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45992</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45992</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44617</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45992</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45961</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45708</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45271</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44918</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44918</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45232</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45933</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46019</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>46019</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>46019</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45688</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45583</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45548</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44985</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46176</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>46177</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45639</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45337</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45302</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>46050</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>46055</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>46182</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44872</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45632</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>46183</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45548</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>46185</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>46189</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45365</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>46191</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>46191</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45305</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44580</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44873</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>44847</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45344</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>46106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46106</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>46106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>46196</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>46198</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>46197</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>46197</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>46197</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>46112</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>46198</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>45470</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>46197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45979</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45565</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45565</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>46202</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46122</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>46122</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45463</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>46202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>46199</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>46203</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>46204</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45098</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45904</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>45709</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45296</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44952</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45552</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>44491</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>46213</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45511</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45278</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45632</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44994</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45477</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45642</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45114</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>45484</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45992</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>46191</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>46230</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>46272</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44943</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>44810</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44873</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45282</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>46279</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44823</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45334</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44790</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45603</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45406</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>46239</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46283</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45162</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>46198</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45494</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>46126</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45246</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>44896</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46246</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45266</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>46245</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>46288</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46246</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>45688</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45016</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>44617</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>44617</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45334</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45495</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45216</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45194</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45448</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45644</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>46296</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46246</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>46254</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>45434</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45772</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45784</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45601</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>46150</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45478</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45791</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45792</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46307</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45525</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>46191</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>46197</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>46191</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45803</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46309</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45782</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46308</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45804</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45805</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>46308</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45808</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45220</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45812</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45222</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>46267</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45561</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>46311</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>46311</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>46267</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46311</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46311</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>45821</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46310</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45505</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45827</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45833</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44741</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45869</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45831</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45874</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45772</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45478</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>44945</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45686</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45792</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45436</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45961</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>45961</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45961</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45960</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>46070</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>46168</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>46178</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>46178</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>46181</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>46185</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45947</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>45624</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46154</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>44969</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>46297</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45425</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45554</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>46178</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>46288</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>45470</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>46247</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>45775</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45944</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>46297</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>46105</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>46272</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>46272</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44552</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>46164</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>46211</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>46309</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>46311</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45819</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45576</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>45600</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>46206</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>46211</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>45789</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>45846</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44671</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45407</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45621</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45980</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>46164</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45574</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>45516</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>45450</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>46195</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45576</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>46311</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45028</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44813</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44487</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45922</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>46147</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>46147</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45922</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>45938</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45944</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45623</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45953</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45960</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>46164</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45993</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45953</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>44832</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>46197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>46197</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>46197</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45793</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>46297</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>46261</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>46304</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>46309</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>46267</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45840</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45847</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45565</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45629</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44868</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>44552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44491</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44491</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44522</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>44825</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44741</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44750</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>44515</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44819</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>44795</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>44813</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44677</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45554</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>45622</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44959</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44795</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44732</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45583</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44728</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44855</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45016</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45552</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44552</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44851</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45576</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45125</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45561</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45220</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45265</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45511</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45280</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45709</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45989</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>44967</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>44895</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45510</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45885</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45895</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45554</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45896</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45334</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45896</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45953</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45874</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45280</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45434</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44494</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45678</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44949</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45580</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45916</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45916</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45919</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>46147</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>44942</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45925</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45925</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45365</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>46148</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45929</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45931</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>46153</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>46150</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45932</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>46153</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>46150</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>46150</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45933</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46150</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45938</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>45938</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>45945</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46154</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45947</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45642</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45957</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45961</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45961</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45960</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45579</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45735</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>46160</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>46160</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>46160</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45607</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>46160</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>46160</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45691</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>45167</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45972</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45973</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45972</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44617</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45975</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45975</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45078</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46163</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45979</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44895</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45068</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>46164</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44910</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45987</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45986</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45987</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45986</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45224</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45992</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45194</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45992</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45992</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45992</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44617</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45992</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45961</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45708</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45271</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44918</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44918</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45232</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45933</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46019</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>46019</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>46019</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45688</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45583</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45548</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44985</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46176</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>46177</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45639</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45337</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45302</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>46050</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>46055</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>46182</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44872</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45632</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>46183</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45548</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>46185</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>46189</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45365</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>46191</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>46191</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45305</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44580</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44873</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>44847</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45344</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>46106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46106</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>46106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>46196</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>46198</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>46197</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>46197</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>46197</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>46112</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>46198</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>45470</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>46197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45979</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45565</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45565</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>46202</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46122</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>46122</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45463</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>46202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>46199</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>46203</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>46204</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45098</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45904</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>45709</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45296</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44952</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45552</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>44491</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>46213</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45511</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45278</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45632</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44994</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45477</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45642</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45114</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>45484</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45992</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>46191</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>46230</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>46272</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44943</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>44810</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44873</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45282</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>46279</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44823</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45334</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44790</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45603</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45406</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>46239</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46283</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45162</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>46198</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45494</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>46126</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45246</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>44896</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46246</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45266</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>46245</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>46288</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46246</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>45688</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45016</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>44617</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>44617</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45334</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45495</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45216</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45194</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45448</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45644</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>46296</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46246</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>46254</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>45434</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45772</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45784</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45601</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>46150</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45478</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45791</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45792</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46307</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45525</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>46191</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>46197</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>46191</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45803</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46309</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45782</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46308</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45804</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45805</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>46308</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45808</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45220</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45812</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45222</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>46267</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45561</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>46311</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>46311</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>46267</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46311</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46311</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>45821</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46310</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45505</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45827</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45833</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44741</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45869</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45831</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45874</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45772</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45478</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>44945</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45686</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45792</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45436</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45961</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>45961</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45961</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45960</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>46070</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>46168</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>46178</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>46178</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>46181</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>46185</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>

--- a/Översikt ÄLVSBYN.xlsx
+++ b/Översikt ÄLVSBYN.xlsx
@@ -601,7 +601,7 @@
         <v>45947</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>46154</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45624</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>45406</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>45320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44497</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46288</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>45226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44969</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45922</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46297</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45894</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45425</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45470</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>46178</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>45554</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>44630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45470</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>46247</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45775</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>46273</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45944</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>46184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>46297</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>46105</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>46272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>46272</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>45573</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>44552</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46164</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>46211</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>45819</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>46309</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>46311</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>46206</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>46211</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>45789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>46261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45600</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45576</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44671</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46164</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>45944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45516</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>46195</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45980</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>45407</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45576</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>46311</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45450</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45574</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45028</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44813</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>46164</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45922</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45944</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45953</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45957</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45960</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>46184</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>46197</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>46197</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>46197</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45989</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45993</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45793</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>45840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>45953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>46297</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>45847</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45565</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45629</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>46304</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>46309</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>46267</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>46314</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45922</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>46147</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46147</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>46150</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45623</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44832</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44868</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44552</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44847</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44825</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44741</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44750</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44602</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44515</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44819</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44795</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44813</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>45885</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45629</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45334</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45334</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>45078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45448</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>44942</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>45896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>45246</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44959</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45603</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>45232</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>46160</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>46163</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44617</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>46164</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>45916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45919</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45114</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>45365</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>44949</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45925</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45925</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45434</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45365</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45932</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>45931</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45933</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45554</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45938</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45125</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45938</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>46177</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>46176</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44952</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45554</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44847</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45946</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45463</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45950</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45947</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>46183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>46182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45957</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>46185</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45960</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45548</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45960</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45961</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45961</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45964</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44872</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>46189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>46191</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44617</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45972</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45972</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>46197</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>46197</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45216</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>46196</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45973</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45974</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45974</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46197</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>46198</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45975</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>46198</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45632</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>46199</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45980</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45220</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>46203</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>46202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45979</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>46202</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45607</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>46204</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45580</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45986</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45986</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45987</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45987</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45579</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45992</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45992</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45992</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45992</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45992</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>46213</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45642</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>46196</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45961</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45992</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46191</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>46230</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45772</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45784</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>46279</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45478</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45601</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>46239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>46019</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>46019</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>46019</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45933</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45688</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45792</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45960</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45791</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45271</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46283</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46288</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46126</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>46198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45525</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46050</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>46246</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>46246</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45782</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45803</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45804</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45805</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>46055</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45808</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45220</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45222</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>45812</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>45561</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45821</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45505</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45477</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46296</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45827</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44873</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45833</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>46246</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>46254</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>46254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45561</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44985</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>46150</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>46106</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>46106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>46106</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44741</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>46112</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>44895</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>44895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45869</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45874</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>46122</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>46122</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>46122</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45831</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>46132</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>46307</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>46308</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45772</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>46308</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>46308</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46191</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>46197</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>45622</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45280</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>46191</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45511</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>46310</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>46267</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>46309</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45709</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>46267</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>46311</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46311</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45552</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45250</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46314</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45510</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>46311</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44580</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45938</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45953</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>46311</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45989</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>44677</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>46314</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45691</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>46314</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45565</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46272</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45334</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45904</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45874</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>44910</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45709</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44943</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>45252</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>46315</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>46317</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>46314</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>46318</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45678</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46314</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46318</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>46318</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45344</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>46148</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>46147</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>46150</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46150</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>46150</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>46150</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>46153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>46154</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45583</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>46153</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>44732</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46160</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>46160</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>46160</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>46160</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44851</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45511</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45162</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45565</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45708</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45078</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45632</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45642</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>44823</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>44494</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45044</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>44810</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45098</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>44967</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>44918</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44918</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44896</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45495</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44873</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45735</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>45576</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>45282</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>44942</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45305</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45639</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45068</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45167</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>45583</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>45552</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45644</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45337</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44552</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45484</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45434</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>44617</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>45194</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44617</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>45194</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44728</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>45224</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>45278</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>44790</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>45280</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45296</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>45251</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>44855</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45016</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45016</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45494</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>44795</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45688</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>45406</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>45302</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>44994</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45548</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>45470</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45478</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>44945</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45686</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45792</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45436</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45960</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>45961</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45961</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>46070</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>46168</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>46178</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>46178</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>46181</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>46185</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
